--- a/artfynd/A 11485-2022 artfynd.xlsx
+++ b/artfynd/A 11485-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11485-2022 artfynd.xlsx
+++ b/artfynd/A 11485-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2070339</v>
+        <v>410484</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547589.2464260483</v>
+        <v>547560</v>
       </c>
       <c r="R2" t="n">
-        <v>7045494.789701759</v>
+        <v>7045641</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1604848</v>
+        <v>486936</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547557.4147348683</v>
+        <v>547618</v>
       </c>
       <c r="R3" t="n">
-        <v>7045472.45257669</v>
+        <v>7045509</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6633306</v>
+        <v>1604848</v>
       </c>
       <c r="B4" t="n">
-        <v>92501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1004672</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547855.5341542157</v>
+        <v>547557</v>
       </c>
       <c r="R4" t="n">
-        <v>7045552.320406716</v>
+        <v>7045472</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6633305</v>
+        <v>1866057</v>
       </c>
       <c r="B5" t="n">
-        <v>92501</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1004672</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547581.8059590393</v>
+        <v>547780</v>
       </c>
       <c r="R5" t="n">
-        <v>7045603.982387075</v>
+        <v>7045634</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1564730</v>
+        <v>1991325</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547836.3396076283</v>
+        <v>547690</v>
       </c>
       <c r="R6" t="n">
-        <v>7045581.030723217</v>
+        <v>7045523</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>486936</v>
+        <v>1991326</v>
       </c>
       <c r="B7" t="n">
-        <v>92505</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2412</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547618.064661234</v>
+        <v>547541</v>
       </c>
       <c r="R7" t="n">
-        <v>7045509.497463686</v>
+        <v>7045619</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1991325</v>
+        <v>2070337</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547689.7867543384</v>
+        <v>547693</v>
       </c>
       <c r="R8" t="n">
-        <v>7045523.063565385</v>
+        <v>7045518</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>410484</v>
+        <v>2070338</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547560.2610935612</v>
+        <v>547563</v>
       </c>
       <c r="R9" t="n">
-        <v>7045640.688937577</v>
+        <v>7045638</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1991326</v>
+        <v>2070339</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547540.9362144682</v>
+        <v>547589</v>
       </c>
       <c r="R10" t="n">
-        <v>7045618.539917124</v>
+        <v>7045495</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,19 +1551,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,32 +1584,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1866057</v>
+        <v>1934435</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547779.7002596698</v>
+        <v>547724</v>
       </c>
       <c r="R11" t="n">
-        <v>7045634.161651707</v>
+        <v>7045468</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,19 +1652,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2070338</v>
+        <v>6633305</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95765</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1004672</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547562.5408779015</v>
+        <v>547582</v>
       </c>
       <c r="R12" t="n">
-        <v>7045637.60013265</v>
+        <v>7045604</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,19 +1753,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2070337</v>
+        <v>6633306</v>
       </c>
       <c r="B13" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95765</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1004672</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547692.9867693228</v>
+        <v>547856</v>
       </c>
       <c r="R13" t="n">
-        <v>7045518.203951262</v>
+        <v>7045552</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2024,19 +1854,9 @@
           <t>2012-06-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,122 +1880,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1934435</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Östra Sörviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>547723.674268981</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7045467.80327352</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2012-06-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 11485-2022 artfynd.xlsx
+++ b/artfynd/A 11485-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/410484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/486936</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1604848</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1866057</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1991325</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1991326</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2070337</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2070338</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2070339</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1934435</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6633305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,8 +1944,27 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6633306</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>